--- a/public/template/report/Template_Rekap.xlsx
+++ b/public/template/report/Template_Rekap.xlsx
@@ -1,42 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahmadmukhtar/Bintang Vet Clinic/bintang-vet-clinic/public/template/report/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE55036-DAA5-A441-B246-A006D3B531E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17140" xr2:uid="{1D77BA03-B59C-2742-B74E-0A357BD26C8B}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="14">
   <si>
     <t>TOTAL KESELURUHAN SISTEM</t>
   </si>
@@ -47,52 +26,62 @@
     <t>UANG MASUK SISTEM</t>
   </si>
   <si>
+    <t>POKOK</t>
+  </si>
+  <si>
+    <t>AKOMODASI</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>DENDA</t>
+  </si>
+  <si>
+    <t>GROOMING</t>
+  </si>
+  <si>
+    <t>OPERASI</t>
+  </si>
+  <si>
+    <t>TOTAL PENGGAJIAN</t>
+  </si>
+  <si>
+    <t>INAP</t>
+  </si>
+  <si>
+    <t>BONUS OMSET</t>
+  </si>
+  <si>
     <t>PENGELUARAN</t>
   </si>
   <si>
-    <t>TOTAL PENGGAJIAN</t>
-  </si>
-  <si>
-    <t>POKOK</t>
-  </si>
-  <si>
-    <t>AKOMODASI</t>
-  </si>
-  <si>
-    <t>OPERASI</t>
-  </si>
-  <si>
-    <t>INAP</t>
-  </si>
-  <si>
-    <t>GROOMING</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>BONUS OMSET</t>
-  </si>
-  <si>
-    <t>DENDA</t>
+    <t>UANG MAKAN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -107,13 +96,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFF2AB84"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -127,70 +116,70 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
@@ -201,31 +190,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="3" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="3" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="1" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="3" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="5" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -272,7 +253,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -324,7 +305,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -385,198 +366,214 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B38AA41-671C-B142-A5DC-D3FC01D548CF}">
-  <dimension ref="A3:Y34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:Y35"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.1640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="true" style="0"/>
+    <col min="2" max="2" width="20.1640625" customWidth="true" style="5"/>
+    <col min="5" max="5" width="22.33203125" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25">
+      <c r="Y1"/>
+    </row>
+    <row r="2" spans="1:25">
+      <c r="Y2"/>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="4"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y3"/>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:25" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Y4"/>
+    </row>
+    <row r="5" spans="1:25" customHeight="1" ht="17">
       <c r="A5" s="1"/>
       <c r="B5" s="4"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y5"/>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="4"/>
       <c r="E6" s="7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -599,11 +596,11 @@
       <c r="X6" s="5"/>
       <c r="Y6" s="5"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="1"/>
       <c r="B7" s="4"/>
       <c r="E7" s="8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -626,13 +623,13 @@
       <c r="X7" s="5"/>
       <c r="Y7" s="5"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>3</v>
-      </c>
+    <row r="8" spans="1:25">
+      <c r="A8" s="3"/>
       <c r="B8" s="4"/>
+      <c r="C8"/>
+      <c r="D8"/>
       <c r="E8" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -655,11 +652,15 @@
       <c r="X8" s="5"/>
       <c r="Y8" s="5"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
+    <row r="9" spans="1:25">
+      <c r="A9" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B9" s="4"/>
+      <c r="C9"/>
+      <c r="D9"/>
       <c r="E9" s="8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -682,13 +683,11 @@
       <c r="X9" s="5"/>
       <c r="Y9" s="5"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>4</v>
-      </c>
+    <row r="10" spans="1:25">
+      <c r="A10" s="1"/>
       <c r="B10" s="4"/>
       <c r="E10" s="8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -711,9 +710,13 @@
       <c r="X10" s="5"/>
       <c r="Y10" s="5"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4"/>
       <c r="E11" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
@@ -736,9 +739,9 @@
       <c r="X11" s="5"/>
       <c r="Y11" s="5"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="E12" s="10" t="s">
-        <v>12</v>
+    <row r="12" spans="1:25">
+      <c r="E12" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
@@ -761,9 +764,9 @@
       <c r="X12" s="5"/>
       <c r="Y12" s="5"/>
     </row>
-    <row r="13" spans="1:25" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E13" s="9" t="s">
-        <v>10</v>
+    <row r="13" spans="1:25">
+      <c r="E13" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -786,26 +789,32 @@
       <c r="X13" s="5"/>
       <c r="Y13" s="5"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="6"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" customHeight="1" ht="17">
+      <c r="E14" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+    </row>
+    <row r="15" spans="1:25">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -823,8 +832,9 @@
       <c r="T15" s="6"/>
       <c r="U15" s="6"/>
       <c r="V15" s="6"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y15"/>
+    </row>
+    <row r="16" spans="1:25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -842,8 +852,9 @@
       <c r="T16" s="6"/>
       <c r="U16" s="6"/>
       <c r="V16" s="6"/>
-    </row>
-    <row r="17" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y16"/>
+    </row>
+    <row r="17" spans="1:25">
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -861,8 +872,9 @@
       <c r="T17" s="6"/>
       <c r="U17" s="6"/>
       <c r="V17" s="6"/>
-    </row>
-    <row r="18" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y17"/>
+    </row>
+    <row r="18" spans="1:25">
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -880,8 +892,9 @@
       <c r="T18" s="6"/>
       <c r="U18" s="6"/>
       <c r="V18" s="6"/>
-    </row>
-    <row r="19" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y18"/>
+    </row>
+    <row r="19" spans="1:25">
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -899,8 +912,9 @@
       <c r="T19" s="6"/>
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
-    </row>
-    <row r="20" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y19"/>
+    </row>
+    <row r="20" spans="1:25">
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -918,8 +932,9 @@
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
       <c r="V20" s="6"/>
-    </row>
-    <row r="21" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y20"/>
+    </row>
+    <row r="21" spans="1:25">
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -937,8 +952,9 @@
       <c r="T21" s="6"/>
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
-    </row>
-    <row r="22" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y21"/>
+    </row>
+    <row r="22" spans="1:25">
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -956,8 +972,9 @@
       <c r="T22" s="6"/>
       <c r="U22" s="6"/>
       <c r="V22" s="6"/>
-    </row>
-    <row r="23" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y22"/>
+    </row>
+    <row r="23" spans="1:25">
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -975,8 +992,9 @@
       <c r="T23" s="6"/>
       <c r="U23" s="6"/>
       <c r="V23" s="6"/>
-    </row>
-    <row r="24" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y23"/>
+    </row>
+    <row r="24" spans="1:25">
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -994,8 +1012,9 @@
       <c r="T24" s="6"/>
       <c r="U24" s="6"/>
       <c r="V24" s="6"/>
-    </row>
-    <row r="25" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y24"/>
+    </row>
+    <row r="25" spans="1:25">
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -1013,8 +1032,9 @@
       <c r="T25" s="6"/>
       <c r="U25" s="6"/>
       <c r="V25" s="6"/>
-    </row>
-    <row r="26" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y25"/>
+    </row>
+    <row r="26" spans="1:25">
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
@@ -1032,8 +1052,9 @@
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
       <c r="V26" s="6"/>
-    </row>
-    <row r="27" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y26"/>
+    </row>
+    <row r="27" spans="1:25">
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
@@ -1051,8 +1072,9 @@
       <c r="T27" s="6"/>
       <c r="U27" s="6"/>
       <c r="V27" s="6"/>
-    </row>
-    <row r="28" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y27"/>
+    </row>
+    <row r="28" spans="1:25">
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
@@ -1070,8 +1092,9 @@
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
       <c r="V28" s="6"/>
-    </row>
-    <row r="29" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y28"/>
+    </row>
+    <row r="29" spans="1:25">
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
@@ -1089,8 +1112,9 @@
       <c r="T29" s="6"/>
       <c r="U29" s="6"/>
       <c r="V29" s="6"/>
-    </row>
-    <row r="30" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y29"/>
+    </row>
+    <row r="30" spans="1:25">
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
@@ -1108,8 +1132,9 @@
       <c r="T30" s="6"/>
       <c r="U30" s="6"/>
       <c r="V30" s="6"/>
-    </row>
-    <row r="31" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y30"/>
+    </row>
+    <row r="31" spans="1:25">
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
@@ -1127,8 +1152,9 @@
       <c r="T31" s="6"/>
       <c r="U31" s="6"/>
       <c r="V31" s="6"/>
-    </row>
-    <row r="32" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y31"/>
+    </row>
+    <row r="32" spans="1:25">
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
@@ -1146,8 +1172,9 @@
       <c r="T32" s="6"/>
       <c r="U32" s="6"/>
       <c r="V32" s="6"/>
-    </row>
-    <row r="33" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y32"/>
+    </row>
+    <row r="33" spans="1:25">
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
@@ -1165,8 +1192,9 @@
       <c r="T33" s="6"/>
       <c r="U33" s="6"/>
       <c r="V33" s="6"/>
-    </row>
-    <row r="34" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="Y33"/>
+    </row>
+    <row r="34" spans="1:25">
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
@@ -1184,8 +1212,40 @@
       <c r="T34" s="6"/>
       <c r="U34" s="6"/>
       <c r="V34" s="6"/>
+      <c r="Y34"/>
+    </row>
+    <row r="35" spans="1:25">
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6"/>
+      <c r="R35" s="6"/>
+      <c r="S35" s="6"/>
+      <c r="T35" s="6"/>
+      <c r="U35" s="6"/>
+      <c r="V35" s="6"/>
+      <c r="Y35"/>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>